--- a/reports/20260727-20260802/熊猫密室周报核对底表_20260727-20260802.xlsx
+++ b/reports/20260727-20260802/熊猫密室周报核对底表_20260727-20260802.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R8fa6063d226d496f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="R502598c26e4b4a28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="Rb5f01864a653482b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="Rbb06b9fc290c4691"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店员全员排名" sheetId="5" r:id="R0b66ed39782e435a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店长排名" sheetId="6" r:id="R4c4a3848a333424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R4e94f85a1cb64278"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="R47b7516212c84ff3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="R9cfad095a0de4028"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="R43cf7f1bf31d40b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店员全员排名" sheetId="5" r:id="R880d47ccbbcc4ca0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店长排名" sheetId="6" r:id="Rbb691774bff14a5d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -527,7 +527,7 @@
         <x:v>新签营收</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>新签营收=总营收-总续卡金额；小程序“新卡金额”只作为卡型原始值留档，不替代新签营收。</x:v>
+        <x:v>一般门店新签营收=总营收-总续卡金额；武汉荟聚按用户2026-08-04确认截图直接使用18,565元。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -551,7 +551,7 @@
         <x:v>卡型率</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>新签小/中/大卡率=对应卡数÷新签卡数；正式19店新签卡609张，卡型277/266/66。</x:v>
+        <x:v>一般门店新签小/中/大卡率=对应卡数÷新签卡数；武汉荟聚按用户确认截图直接使用41%/45%/4%。正式19店新签卡609张。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -709,7 +709,7 @@
         <x:v>2126</x:v>
       </x:c>
       <x:c r="I2" s="11" t="n">
-        <x:v>295571.3</x:v>
+        <x:v>286993.25</x:v>
       </x:c>
       <x:c r="J2" s="4" t="n">
         <x:v>783</x:v>
@@ -745,7 +745,7 @@
         <x:v>0.08184383819379114</x:v>
       </x:c>
       <x:c r="U2" s="11" t="n">
-        <x:v>79136.6</x:v>
+        <x:v>82636.6</x:v>
       </x:c>
       <x:c r="V2" s="11" t="n">
         <x:v>166698.75000000003</x:v>
@@ -922,7 +922,7 @@
         <x:v>489</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
-        <x:v>91700.54999999999</x:v>
+        <x:v>83122.5</x:v>
       </x:c>
       <x:c r="J5" s="4" t="n">
         <x:v>213</x:v>
@@ -958,7 +958,7 @@
         <x:v>0.07975460122699386</x:v>
       </x:c>
       <x:c r="U5" s="11" t="n">
-        <x:v>18500</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="V5" s="11" t="n">
         <x:v>69289.5</x:v>
@@ -970,7 +970,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b40ee03e2d449a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41b08b3736914787"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1349,7 +1349,7 @@
         <x:v>-0.005394623584718292</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
-        <x:v>27143.05</x:v>
+        <x:v>18565</x:v>
       </x:c>
       <x:c r="J5" s="4" t="n">
         <x:v>55</x:v>
@@ -1370,16 +1370,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="P5" s="13" t="n">
-        <x:v>0.40816326530612246</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="Q5" s="12" t="n">
-        <x:v>0.46938775510204084</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="R5" s="12" t="n">
-        <x:v>0.12244897959183673</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="S5" s="12" t="n">
-        <x:v>0.5052</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="T5" s="4" t="n">
         <x:v>6</x:v>
@@ -1388,7 +1388,7 @@
         <x:v>0.07139999999999999</x:v>
       </x:c>
       <x:c r="V5" s="11" t="n">
-        <x:v>2900</x:v>
+        <x:v>6400</x:v>
       </x:c>
       <x:c r="W5" s="11" t="n">
         <x:v>16847</x:v>
@@ -1397,10 +1397,10 @@
         <x:v>7407</x:v>
       </x:c>
       <x:c r="Y5" s="14" t="str">
-        <x:v>完成率68.34%&lt;100%；新签小卡率40.82%&gt;40%</x:v>
+        <x:v>完成率68.34%&lt;100%；新签小卡率41.00%&gt;40%</x:v>
       </x:c>
       <x:c r="Z5" s="4" t="str">
-        <x:v>新签营收=总营收-总续卡金额；新客数按本周截图/底表；老客数按本周会员数据口径；总引流和扫楼取用户确认截图</x:v>
+        <x:v>用户2026-08-04确认截图直接覆盖：新签营收18565、新签办卡率46%、新签小/中/大卡率41%/45%/4%、续卡金额6400。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2606,7 +2606,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5266e528aa214200"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree077f478bab40d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4208,7 +4208,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf61e30c7683c4fa7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c6a04d5bfb84dba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6812,7 +6812,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9db5157c3b094aa5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a2e98fbfc244c93"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8130,7 +8130,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c48fd228a5445d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R645ce2c176954a3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>